--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260708.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>19,670,000</t>
+          <t>16,551,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>16,551,000</t>
+          <t>19,670,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,986,000</t>
+          <t>26,770,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>26,770,000</t>
+          <t>16,986,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>16,596,000</t>
+          <t>10,069,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,218,000</t>
+          <t>16,596,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>10,069,000</t>
+          <t>2,218,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>5,317,000</t>
+          <t>15,048,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>15,048,000</t>
+          <t>5,317,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
